--- a/data/trans_orig/P79A6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A6_2023-Provincia-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>836</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>73,98%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41105</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>926</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30428</t>
+          <t>37953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23639</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>64508</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>64508</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>64508</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>163530</t>
+          <t>192779</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>184619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168357</t>
+          <t>198420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>180983</t>
+          <t>209216</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175505</t>
+          <t>202994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184219</t>
+          <t>212839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>344513</t>
+          <t>401994</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>335638</t>
+          <t>392232</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>350519</t>
+          <t>408786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>359665</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>359665</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>359665</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>220010</t>
+          <t>256037</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>207996</t>
+          <t>242453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229921</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>257146</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>238496</t>
+          <t>279280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>270105</t>
+          <t>310830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>552961</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>455883</t>
+          <t>533348</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>569764</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>77678</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
